--- a/data/trans_orig/IP1002-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP1002-Clase-trans_orig.xlsx
@@ -738,7 +738,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4237</t>
+          <t>4401</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -808,7 +808,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>4175</t>
+          <t>4502</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,23%</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>100115</t>
+          <t>99951</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,94%</t>
+          <t>95,78%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -916,7 +916,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>197723</t>
+          <t>197396</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,93%</t>
+          <t>97,77%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5321</t>
+          <t>4190</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5287</t>
+          <t>5243</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1131,7 +1131,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>708</t>
+          <t>844</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>6790</t>
+          <t>6990</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>4,03%</t>
         </is>
       </c>
     </row>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>82068</t>
+          <t>83199</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>93,91%</t>
+          <t>95,21%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1224,7 +1224,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>80683</t>
+          <t>80727</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>93,85%</t>
+          <t>93,9%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>166569</t>
+          <t>166369</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>172651</t>
+          <t>172515</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,08%</t>
+          <t>95,97%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,59%</t>
+          <t>99,51%</t>
         </is>
       </c>
     </row>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>3229</t>
+          <t>3863</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1459,7 +1459,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>4028</t>
+          <t>4206</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1494,7 +1494,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>4790</t>
+          <t>4622</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1509,7 +1509,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,77%</t>
         </is>
       </c>
     </row>
@@ -1532,7 +1532,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>64163</t>
+          <t>63529</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,21%</t>
+          <t>94,27%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1567,7 +1567,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>95304</t>
+          <t>95126</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,94%</t>
+          <t>95,77%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1602,7 +1602,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>161934</t>
+          <t>162102</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,13%</t>
+          <t>97,23%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>639</t>
+          <t>636</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5927</t>
+          <t>5947</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1472</t>
+          <t>1885</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>8902</t>
+          <t>8700</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3305</t>
+          <t>3190</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>11825</t>
+          <t>11579</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,87%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>194806</t>
+          <t>194786</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>200094</t>
+          <t>200097</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,05%</t>
+          <t>97,04%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>193172</t>
+          <t>193374</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>200602</t>
+          <t>200189</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,59%</t>
+          <t>95,69%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,27%</t>
+          <t>99,07%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>390982</t>
+          <t>391228</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>399502</t>
+          <t>399617</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,06%</t>
+          <t>97,13%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,18%</t>
+          <t>99,21%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>632</t>
+          <t>864</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>6761</t>
+          <t>6742</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2145,7 +2145,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>3602</t>
+          <t>3641</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2160,7 +2160,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1260</t>
+          <t>1218</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>8146</t>
+          <t>8364</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,61%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>97359</t>
+          <t>97378</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>103488</t>
+          <t>103256</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>93,51%</t>
+          <t>93,52%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,39%</t>
+          <t>99,17%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,7 +2253,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>123687</t>
+          <t>123648</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -2268,7 +2268,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>97,17%</t>
+          <t>97,14%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>223264</t>
+          <t>223046</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>230150</t>
+          <t>230192</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,48%</t>
+          <t>96,39%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,46%</t>
+          <t>99,47%</t>
         </is>
       </c>
     </row>
@@ -2488,7 +2488,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>3641</t>
+          <t>4321</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2503,7 +2503,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>5,97%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2523,7 +2523,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>4105</t>
+          <t>4050</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,75%</t>
         </is>
       </c>
     </row>
@@ -2596,7 +2596,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>68751</t>
+          <t>68071</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -2611,7 +2611,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>94,97%</t>
+          <t>94,03%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>143157</t>
+          <t>143212</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>97,21%</t>
+          <t>97,25%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>4620</t>
+          <t>4301</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>14180</t>
+          <t>13632</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>3972</t>
+          <t>4031</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>14439</t>
+          <t>13485</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>10720</t>
+          <t>10422</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>23794</t>
+          <t>23671</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,79%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>624676</t>
+          <t>625224</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>634236</t>
+          <t>634555</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>97,78%</t>
+          <t>97,87%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,28%</t>
+          <t>99,33%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>670164</t>
+          <t>671118</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>680631</t>
+          <t>680572</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>97,89%</t>
+          <t>98,03%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>99,42%</t>
+          <t>99,41%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1299665</t>
+          <t>1299788</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1312739</t>
+          <t>1313037</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>98,2%</t>
+          <t>98,21%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,19%</t>
+          <t>99,21%</t>
         </is>
       </c>
     </row>
@@ -3373,7 +3373,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3358</t>
+          <t>3162</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3388,7 +3388,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3408,7 +3408,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4022</t>
+          <t>3732</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3423,7 +3423,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3443,7 +3443,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>4731</t>
+          <t>4783</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3458,7 +3458,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,68%</t>
         </is>
       </c>
     </row>
@@ -3481,7 +3481,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>85081</t>
+          <t>85277</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,2%</t>
+          <t>96,42%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -3516,7 +3516,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>85741</t>
+          <t>86031</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,52%</t>
+          <t>95,84%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -3551,7 +3551,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>173472</t>
+          <t>173420</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,35%</t>
+          <t>97,32%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3200</t>
+          <t>2864</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3731,7 +3731,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3746,12 +3746,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>663</t>
+          <t>662</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5313</t>
+          <t>6043</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3766,7 +3766,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>6,29%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>675</t>
+          <t>672</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>6566</t>
+          <t>7162</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3801,7 +3801,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,79%</t>
         </is>
       </c>
     </row>
@@ -3824,7 +3824,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>89529</t>
+          <t>89865</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -3839,7 +3839,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,55%</t>
+          <t>96,91%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>90798</t>
+          <t>90068</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>95448</t>
+          <t>95449</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3874,7 +3874,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,47%</t>
+          <t>93,71%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>182274</t>
+          <t>181678</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>188165</t>
+          <t>188168</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3909,7 +3909,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,52%</t>
+          <t>96,21%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -4059,7 +4059,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4547</t>
+          <t>5262</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4094,7 +4094,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>4211</t>
+          <t>4414</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4109,7 +4109,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>635</t>
+          <t>671</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>6123</t>
+          <t>6590</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4139,12 +4139,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,85%</t>
         </is>
       </c>
     </row>
@@ -4167,7 +4167,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>79658</t>
+          <t>78943</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -4182,7 +4182,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,6%</t>
+          <t>93,75%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -4202,7 +4202,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>82679</t>
+          <t>82476</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -4217,7 +4217,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,15%</t>
+          <t>94,92%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>164972</t>
+          <t>164505</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>170460</t>
+          <t>170424</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,42%</t>
+          <t>96,15%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,63%</t>
+          <t>99,61%</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>1904</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>9254</t>
+          <t>9139</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5332</t>
+          <t>5243</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>16296</t>
+          <t>15746</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>6,94%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>8883</t>
+          <t>9123</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>21814</t>
+          <t>22208</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>5,13%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>196374</t>
+          <t>196489</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>203606</t>
+          <t>203724</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,5%</t>
+          <t>95,56%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,02%</t>
+          <t>99,07%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>210568</t>
+          <t>211118</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>221532</t>
+          <t>221621</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>92,82%</t>
+          <t>93,06%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,65%</t>
+          <t>97,69%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>410678</t>
+          <t>410284</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>423609</t>
+          <t>423369</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,96%</t>
+          <t>94,87%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,95%</t>
+          <t>97,89%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1348</t>
+          <t>1273</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>8113</t>
+          <t>8041</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4780,7 +4780,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>5374</t>
+          <t>4844</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4795,7 +4795,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2080</t>
+          <t>2144</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>9496</t>
+          <t>9614</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,33%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>141056</t>
+          <t>141128</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>147821</t>
+          <t>147896</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>94,56%</t>
+          <t>94,61%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,1%</t>
+          <t>99,15%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4888,7 +4888,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>134460</t>
+          <t>134990</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -4903,7 +4903,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>96,16%</t>
+          <t>96,54%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>279507</t>
+          <t>279389</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>286923</t>
+          <t>286859</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,71%</t>
+          <t>96,67%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,28%</t>
+          <t>99,26%</t>
         </is>
       </c>
     </row>
@@ -5123,7 +5123,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>4377</t>
+          <t>4641</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5138,7 +5138,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5158,7 +5158,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>4916</t>
+          <t>4697</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5173,7 +5173,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,67%</t>
         </is>
       </c>
     </row>
@@ -5231,7 +5231,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>69661</t>
+          <t>69397</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -5246,7 +5246,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>94,09%</t>
+          <t>93,73%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -5266,7 +5266,7 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>123033</t>
+          <t>123252</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
@@ -5281,7 +5281,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>96,16%</t>
+          <t>96,33%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>6544</t>
+          <t>5987</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>17490</t>
+          <t>17027</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>10705</t>
+          <t>10719</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>24470</t>
+          <t>24458</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>20155</t>
+          <t>19447</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>37843</t>
+          <t>36892</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,66%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>656591</t>
+          <t>657054</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>667537</t>
+          <t>668094</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>97,41%</t>
+          <t>97,47%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,03%</t>
+          <t>99,11%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>689031</t>
+          <t>689043</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>702796</t>
+          <t>702782</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1349739</t>
+          <t>1350690</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1367427</t>
+          <t>1368135</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>97,27%</t>
+          <t>97,34%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>98,55%</t>
+          <t>98,6%</t>
         </is>
       </c>
     </row>
@@ -6008,7 +6008,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2808</t>
+          <t>2751</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6023,7 +6023,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6038,12 +6038,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>630</t>
+          <t>637</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6064</t>
+          <t>5419</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6073,12 +6073,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>683</t>
+          <t>635</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>5754</t>
+          <t>6280</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6088,12 +6088,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,43%</t>
         </is>
       </c>
     </row>
@@ -6116,7 +6116,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>80282</t>
+          <t>80339</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -6131,7 +6131,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,62%</t>
+          <t>96,69%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -6151,12 +6151,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>93733</t>
+          <t>94378</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>99167</t>
+          <t>99160</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,92%</t>
+          <t>94,57%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,37%</t>
+          <t>99,36%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6186,12 +6186,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>177133</t>
+          <t>176607</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>182204</t>
+          <t>182252</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,85%</t>
+          <t>96,57%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,63%</t>
+          <t>99,65%</t>
         </is>
       </c>
     </row>
@@ -6386,7 +6386,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4645</t>
+          <t>4785</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6401,7 +6401,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6421,7 +6421,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>5028</t>
+          <t>5358</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6436,7 +6436,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,45%</t>
         </is>
       </c>
     </row>
@@ -6494,7 +6494,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>108101</t>
+          <t>107961</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -6509,7 +6509,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,88%</t>
+          <t>95,76%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -6529,7 +6529,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>213432</t>
+          <t>213102</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -6544,7 +6544,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,7%</t>
+          <t>97,55%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -6729,7 +6729,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>3800</t>
+          <t>3178</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6744,7 +6744,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6764,7 +6764,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>3167</t>
+          <t>3182</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6779,7 +6779,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,32%</t>
         </is>
       </c>
     </row>
@@ -6837,7 +6837,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>71628</t>
+          <t>72250</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -6852,7 +6852,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,96%</t>
+          <t>95,79%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -6872,7 +6872,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>134101</t>
+          <t>134086</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -6887,7 +6887,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,69%</t>
+          <t>97,68%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -7032,12 +7032,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1892</t>
+          <t>1963</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>8978</t>
+          <t>9517</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7047,12 +7047,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>628</t>
+          <t>631</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5675</t>
+          <t>6280</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7087,7 +7087,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7102,12 +7102,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3699</t>
+          <t>3620</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>12280</t>
+          <t>12076</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,78%</t>
         </is>
       </c>
     </row>
@@ -7145,12 +7145,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>214599</t>
+          <t>214060</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>221685</t>
+          <t>221614</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,98%</t>
+          <t>95,74%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,15%</t>
+          <t>99,12%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7180,12 +7180,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>205179</t>
+          <t>204574</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>210226</t>
+          <t>210223</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7195,7 +7195,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,31%</t>
+          <t>97,02%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -7215,12 +7215,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>422151</t>
+          <t>422355</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>430732</t>
+          <t>430811</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,17%</t>
+          <t>97,22%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,15%</t>
+          <t>99,17%</t>
         </is>
       </c>
     </row>
@@ -7375,12 +7375,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>602</t>
+          <t>609</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>5994</t>
+          <t>6142</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7390,12 +7390,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7410,12 +7410,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>648</t>
+          <t>650</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>5868</t>
+          <t>5668</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7430,7 +7430,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7445,12 +7445,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1590</t>
+          <t>1475</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>8825</t>
+          <t>8681</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,11%</t>
         </is>
       </c>
     </row>
@@ -7488,12 +7488,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>130200</t>
+          <t>130052</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>135592</t>
+          <t>135585</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7503,12 +7503,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,6%</t>
+          <t>95,49%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,56%</t>
+          <t>99,55%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>137220</t>
+          <t>137420</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>142440</t>
+          <t>142438</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7538,7 +7538,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,9%</t>
+          <t>96,04%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -7558,12 +7558,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>270457</t>
+          <t>270601</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>277692</t>
+          <t>277807</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,84%</t>
+          <t>96,89%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,43%</t>
+          <t>99,47%</t>
         </is>
       </c>
     </row>
@@ -7723,7 +7723,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3041</t>
+          <t>2327</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7738,7 +7738,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7758,7 +7758,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>4281</t>
+          <t>2721</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7773,7 +7773,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7793,7 +7793,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>3770</t>
+          <t>3752</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7808,7 +7808,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,91%</t>
         </is>
       </c>
     </row>
@@ -7831,7 +7831,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>58046</t>
+          <t>58760</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -7846,7 +7846,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>95,02%</t>
+          <t>96,19%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -7866,7 +7866,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>63544</t>
+          <t>65104</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -7881,7 +7881,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>93,69%</t>
+          <t>95,99%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -7901,7 +7901,7 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>125142</t>
+          <t>125160</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
@@ -7916,7 +7916,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>97,08%</t>
+          <t>97,09%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -8061,12 +8061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>4067</t>
+          <t>4234</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>13508</t>
+          <t>13572</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8096,12 +8096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>5328</t>
+          <t>5211</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>14615</t>
+          <t>15460</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8131,12 +8131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>11463</t>
+          <t>11184</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>24919</t>
+          <t>24478</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8146,12 +8146,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,77%</t>
         </is>
       </c>
     </row>
@@ -8174,12 +8174,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>657994</t>
+          <t>657930</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>667435</t>
+          <t>667268</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>97,99%</t>
+          <t>97,98%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,39%</t>
+          <t>99,37%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>695122</t>
+          <t>694277</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>704409</t>
+          <t>704526</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>97,94%</t>
+          <t>97,82%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>99,25%</t>
+          <t>99,27%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8244,12 +8244,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1356320</t>
+          <t>1356761</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1369776</t>
+          <t>1370055</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8259,12 +8259,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>98,2%</t>
+          <t>98,23%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,17%</t>
+          <t>99,19%</t>
         </is>
       </c>
     </row>
@@ -8638,12 +8638,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>607</t>
+          <t>602</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6490</t>
+          <t>6020</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8658,7 +8658,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8678,7 +8678,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>1845</t>
+          <t>2369</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8693,7 +8693,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8708,12 +8708,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1121</t>
+          <t>1122</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>7200</t>
+          <t>7295</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8728,7 +8728,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>3,02%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>97972</t>
+          <t>98442</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>103855</t>
+          <t>103860</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8766,7 +8766,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,79%</t>
+          <t>94,24%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -8786,7 +8786,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>135063</t>
+          <t>134539</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -8801,7 +8801,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>98,65%</t>
+          <t>98,27%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>234170</t>
+          <t>234075</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>240249</t>
+          <t>240248</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8836,7 +8836,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,02%</t>
+          <t>96,98%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -8986,7 +8986,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2142</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -9001,7 +9001,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9016,12 +9016,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>860</t>
+          <t>856</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>9517</t>
+          <t>10334</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -9036,7 +9036,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,96%</t>
+          <t>10,81%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9051,12 +9051,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1262</t>
+          <t>853</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>9421</t>
+          <t>10251</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -9066,12 +9066,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>5,39%</t>
         </is>
       </c>
     </row>
@@ -9094,7 +9094,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>92539</t>
+          <t>92337</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -9109,7 +9109,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,74%</t>
+          <t>97,52%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>86056</t>
+          <t>85239</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>94713</t>
+          <t>94717</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -9144,7 +9144,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>90,04%</t>
+          <t>89,19%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>180833</t>
+          <t>180003</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>188992</t>
+          <t>189401</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,05%</t>
+          <t>94,61%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,34%</t>
+          <t>99,55%</t>
         </is>
       </c>
     </row>
@@ -9364,7 +9364,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>7302</t>
+          <t>8314</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9379,7 +9379,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>11,44%</t>
+          <t>13,02%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9399,7 +9399,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>6710</t>
+          <t>8947</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9414,7 +9414,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>7,73%</t>
         </is>
       </c>
     </row>
@@ -9472,7 +9472,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>56551</t>
+          <t>55539</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -9487,7 +9487,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>88,56%</t>
+          <t>86,98%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -9507,7 +9507,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>109004</t>
+          <t>106767</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -9522,7 +9522,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,2%</t>
+          <t>92,27%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -9667,12 +9667,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>751</t>
+          <t>816</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7974</t>
+          <t>8305</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9682,12 +9682,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9702,12 +9702,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>806</t>
+          <t>802</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>7425</t>
+          <t>7561</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9722,7 +9722,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9737,12 +9737,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2492</t>
+          <t>2419</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>11869</t>
+          <t>11283</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9752,12 +9752,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,59%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>210036</t>
+          <t>209705</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>217259</t>
+          <t>217194</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,34%</t>
+          <t>96,19%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,66%</t>
+          <t>99,63%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>209844</t>
+          <t>209708</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>216463</t>
+          <t>216467</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9830,7 +9830,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,58%</t>
+          <t>96,52%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>423410</t>
+          <t>423996</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>432787</t>
+          <t>432860</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,27%</t>
+          <t>97,41%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,43%</t>
+          <t>99,44%</t>
         </is>
       </c>
     </row>
@@ -10010,12 +10010,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>393</t>
+          <t>405</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>6725</t>
+          <t>6145</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10025,12 +10025,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10045,12 +10045,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>391</t>
+          <t>394</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>6071</t>
+          <t>5361</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -10065,7 +10065,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10080,12 +10080,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1671</t>
+          <t>1506</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>9719</t>
+          <t>8999</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -10095,12 +10095,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,19%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>112703</t>
+          <t>113283</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>119035</t>
+          <t>119023</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>94,37%</t>
+          <t>94,85%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,67%</t>
+          <t>99,66%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>156546</t>
+          <t>157256</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>162226</t>
+          <t>162223</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10173,7 +10173,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>96,27%</t>
+          <t>96,7%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>272326</t>
+          <t>273046</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>280374</t>
+          <t>280539</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,55%</t>
+          <t>96,81%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,41%</t>
+          <t>99,47%</t>
         </is>
       </c>
     </row>
@@ -10358,7 +10358,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>2433</t>
+          <t>2229</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -10373,7 +10373,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10393,7 +10393,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>3969</t>
+          <t>4358</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -10408,7 +10408,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>6,05%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10428,7 +10428,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>4922</t>
+          <t>4546</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -10443,7 +10443,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,23%</t>
         </is>
       </c>
     </row>
@@ -10466,7 +10466,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>66462</t>
+          <t>66666</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -10481,7 +10481,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>96,47%</t>
+          <t>96,76%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -10501,7 +10501,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>68034</t>
+          <t>67645</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -10516,7 +10516,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>94,49%</t>
+          <t>93,95%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -10536,7 +10536,7 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>135976</t>
+          <t>136352</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
@@ -10551,7 +10551,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>96,51%</t>
+          <t>96,77%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -10696,12 +10696,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>4862</t>
+          <t>4440</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>15632</t>
+          <t>14243</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10711,47 +10711,47 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
+          <t>0,68%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>2,17%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>10656</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>5551</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>20229</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>1,42%</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
           <t>0,74%</t>
         </is>
       </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>2,38%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>10656</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>5784</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>18299</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>1,42%</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>0,77%</t>
-        </is>
-      </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10766,12 +10766,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>12283</t>
+          <t>12704</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>28858</t>
+          <t>28012</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10781,12 +10781,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>1,99%</t>
         </is>
       </c>
     </row>
@@ -10809,12 +10809,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>641705</t>
+          <t>643094</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>652475</t>
+          <t>652897</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10824,49 +10824,49 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>97,62%</t>
+          <t>97,83%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
+          <t>99,32%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>946</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>737567</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>727994</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>742672</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>98,58%</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>97,3%</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
           <t>99,26%</t>
         </is>
       </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>946</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>737567</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>729924</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>742439</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>98,58%</t>
-        </is>
-      </c>
-      <c r="O23" s="2" t="inlineStr">
-        <is>
-          <t>97,55%</t>
-        </is>
-      </c>
-      <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t>99,23%</t>
-        </is>
-      </c>
       <c r="Q23" s="2" t="inlineStr">
         <is>
           <t>1862</t>
@@ -10879,12 +10879,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1376702</t>
+          <t>1377548</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1393277</t>
+          <t>1392856</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10894,12 +10894,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>97,95%</t>
+          <t>98,01%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,13%</t>
+          <t>99,1%</t>
         </is>
       </c>
     </row>
